--- a/day_to_day_update.xlsx
+++ b/day_to_day_update.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3b759879550385cf/Desktop/SkillHub_WebDev/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satyasrinivaskola\OneDrive\Desktop\SkillHub_WebDev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="112" documentId="13_ncr:1_{0DB8EED8-B121-4BAE-90F5-8665FE03036C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EE318C8-35ED-40DF-818D-5E4D1E485391}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC832975-9AB2-412B-9B0B-A92CE063ACB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="76">
   <si>
     <t>Date</t>
   </si>
@@ -276,6 +276,88 @@
 Hover,
 scale,Translate,cursor
 </t>
+  </si>
+  <si>
+    <t>Given one Mini project flats booking and assisted</t>
+  </si>
+  <si>
+    <t>Continuing the Mini project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Explained git and github and
+Installed Git 
+solved doubt while creating github account and 
+export files to github  and created first repo  configuration setup
+</t>
+  </si>
+  <si>
+    <t>Created one project using hover and psudeclasses and 
+elements</t>
+  </si>
+  <si>
+    <t>Explained remaing use tags like mark and bold and 
+marquee 12 tags</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Explained about nth-child and nth-elements </t>
+  </si>
+  <si>
+    <t>Done pendnng works along with one project related to
+Positions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Explained Function types and created </t>
+  </si>
+  <si>
+    <t>Explained string data types  and methods(indexof,
+trim,replace,empty string,length)</t>
+  </si>
+  <si>
+    <t>Explained array methods</t>
+  </si>
+  <si>
+    <t>Explained array methods and tried</t>
+  </si>
+  <si>
+    <t>Holiday</t>
+  </si>
+  <si>
+    <t>Explained Js to Basics array,functions</t>
+  </si>
+  <si>
+    <t>Explained &amp;Revised all topics HTML,CSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assistance the Projects and </t>
+  </si>
+  <si>
+    <t>Explained Math methods and appenchild and createElement
+,removechild,classList.add,classList.remove().</t>
+  </si>
+  <si>
+    <t>Sunday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ParseInt,Schedulars and Arrow funtion </t>
+  </si>
+  <si>
+    <t>Given task based on Js and assisted (Task:
+take two numbers from user and select maximum number and decrese it untliii zero)</t>
+  </si>
+  <si>
+    <t>continued project and showed and explained full code and conditional operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">querySelector,querySelectorAll,getElementByTagName
+getElementByClassListName,destructuring array and object destructuring,array reduce method
+While and do while loops,Rest and spread operator
+</t>
+  </si>
+  <si>
+    <t>Eventd in JS inline,onevents,Addeventlisteners</t>
+  </si>
+  <si>
+    <t>Practicing one projects based on events and assisted</t>
   </si>
 </sst>
 </file>
@@ -351,7 +433,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -369,6 +451,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -666,10 +753,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -933,12 +1016,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="42.1796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.6328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="36.26953125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="45.1796875" customWidth="1"/>
@@ -1244,6 +1326,220 @@
       </c>
       <c r="B19" s="3" t="s">
         <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="5">
+        <v>46138</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="5">
+        <v>46139</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="5">
+        <v>46140</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="5">
+        <v>46141</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="87" x14ac:dyDescent="0.35">
+      <c r="A24" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="5">
+        <v>46143</v>
+      </c>
+      <c r="B25" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="5">
+        <v>46144</v>
+      </c>
+      <c r="B26" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="9">
+        <v>46145</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="5">
+        <v>46146</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="5">
+        <v>46147</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="5">
+        <v>46148</v>
+      </c>
+      <c r="B30" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="5">
+        <v>46149</v>
+      </c>
+      <c r="B31" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="5">
+        <v>46150</v>
+      </c>
+      <c r="B32" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="9">
+        <v>46151</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" s="9">
+        <v>46152</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="9">
+        <v>46153</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="5">
+        <v>46154</v>
+      </c>
+      <c r="B36" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A37" s="5">
+        <v>46155</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A38" s="5">
+        <v>46156</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" s="5">
+        <v>46157</v>
+      </c>
+      <c r="B39" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A40" s="5">
+        <v>46158</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" s="5">
+        <v>46159</v>
+      </c>
+      <c r="B41" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A42" s="5">
+        <v>46160</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" s="5">
+        <v>46161</v>
+      </c>
+      <c r="B43" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A44" s="5">
+        <v>46162</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A45" s="5">
+        <v>46163</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/day_to_day_update.xlsx
+++ b/day_to_day_update.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satyasrinivaskola\OneDrive\Desktop\SkillHub_WebDev\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3b759879550385cf/Desktop/SkillHub_WebDev/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC832975-9AB2-412B-9B0B-A92CE063ACB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{DC832975-9AB2-412B-9B0B-A92CE063ACB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{689AF4CF-3A5E-4D2A-ACCD-3B2386BD637D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="80">
   <si>
     <t>Date</t>
   </si>
@@ -358,6 +358,20 @@
   </si>
   <si>
     <t>Practicing one projects based on events and assisted</t>
+  </si>
+  <si>
+    <t>Api fetching Methods in Js</t>
+  </si>
+  <si>
+    <t>Revised all topics</t>
+  </si>
+  <si>
+    <t>Spread ,reduce in array,closures,hoisting ,stoppropagation
+capturing,bubbling</t>
+  </si>
+  <si>
+    <t>Explained how stament get executed ,global execution context and 
+call back stack and queue ans microtask queue</t>
   </si>
 </sst>
 </file>
@@ -1016,7 +1030,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.08984375" bestFit="1" customWidth="1"/>
@@ -1540,6 +1554,66 @@
       </c>
       <c r="B45" s="3" t="s">
         <v>73</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A46" s="5">
+        <v>46164</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A47" s="5">
+        <v>46165</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" s="5">
+        <v>46166</v>
+      </c>
+      <c r="B48" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" s="5">
+        <v>46167</v>
+      </c>
+      <c r="B49" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" s="5">
+        <v>46168</v>
+      </c>
+      <c r="B50" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" s="5">
+        <v>46169</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" s="5">
+        <v>46170</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" s="5">
+        <v>46171</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" s="5">
+        <v>46172</v>
       </c>
     </row>
   </sheetData>
